--- a/docs/TCS-Agentic-AI-Agent-Catalog.xlsx
+++ b/docs/TCS-Agentic-AI-Agent-Catalog.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1927" uniqueCount="590">
   <si>
     <t>TCS Agentic AI — Agent Catalog</t>
   </si>
   <si>
-    <t>15 agents · 177 tools. Each row is a complete, connectable MCP endpoint — nothing to assemble.</t>
+    <t>16 agents · 189 tools. Each row is a complete, connectable MCP endpoint — nothing to assemble.</t>
   </si>
   <si>
     <t>Agent</t>
@@ -122,6 +122,15 @@
     <t>https://mcp-dashboard-openshift-mcp.apps.openshift.caaslab.local/mcp/vm-lifecycle/sse</t>
   </si>
   <si>
+    <t>VM Migration Agent</t>
+  </si>
+  <si>
+    <t>vm-migration</t>
+  </si>
+  <si>
+    <t>https://mcp-dashboard-openshift-mcp.apps.openshift.caaslab.local/mcp/vm-migration/sse</t>
+  </si>
+  <si>
     <t>Cluster Operations Agent</t>
   </si>
   <si>
@@ -194,7 +203,7 @@
     <t>Connect with GET on the URL above. The SSE stream issues a sessionId; replies go to the same path with /message?sessionId=&lt;id&gt;. Connecting to the bare /mcp/&lt;agent-id&gt; returns 404 — the transport lives on /sse.</t>
   </si>
   <si>
-    <t>The whole registry is also reachable as one MCP server at https://mcp-dashboard-openshift-mcp.apps.openshift.caaslab.local/sse, carrying all 177 tools. Prefer a specific agent — a focused tool list measurably improves tool selection.</t>
+    <t>The whole registry is also reachable as one MCP server at https://mcp-dashboard-openshift-mcp.apps.openshift.caaslab.local/sse, carrying all 189 tools. Prefer a specific agent — a focused tool list measurably improves tool selection.</t>
   </si>
   <si>
     <t>Every endpoint, per agent</t>
@@ -260,6 +269,12 @@
     <t>https://mcp-dashboard-openshift-mcp.apps.openshift.caaslab.local/api/agents/vm-lifecycle/tools</t>
   </si>
   <si>
+    <t>https://mcp-dashboard-openshift-mcp.apps.openshift.caaslab.local/mcp/vm-migration/message</t>
+  </si>
+  <si>
+    <t>https://mcp-dashboard-openshift-mcp.apps.openshift.caaslab.local/api/agents/vm-migration/tools</t>
+  </si>
+  <si>
     <t>https://mcp-dashboard-openshift-mcp.apps.openshift.caaslab.local/mcp/cluster-operations/message</t>
   </si>
   <si>
@@ -305,7 +320,7 @@
     <t>The MCP client library performs the SSE handshake for you — you supply the SSE URL only. The message URL is listed because proxy and firewall rules must permit both.</t>
   </si>
   <si>
-    <t>All 177 tools, and the agent that carries each</t>
+    <t>All 189 tools, and the agent that carries each</t>
   </si>
   <si>
     <t>Filter or sort this sheet to find the tool you need, then connect to the agent in the last column.</t>
@@ -545,6 +560,42 @@
     <t>kubevirt_list_vmis</t>
   </si>
   <si>
+    <t>mtv_readiness_check</t>
+  </si>
+  <si>
+    <t>mtv_list_providers</t>
+  </si>
+  <si>
+    <t>mtv_list_maps</t>
+  </si>
+  <si>
+    <t>mtv_discover_vms</t>
+  </si>
+  <si>
+    <t>mtv_plan_preview</t>
+  </si>
+  <si>
+    <t>mtv_create_plans</t>
+  </si>
+  <si>
+    <t>mtv_plan_status</t>
+  </si>
+  <si>
+    <t>mtv_start_migration</t>
+  </si>
+  <si>
+    <t>mtv_migration_progress</t>
+  </si>
+  <si>
+    <t>mtv_rollback_preview</t>
+  </si>
+  <si>
+    <t>mtv_rollback_migration</t>
+  </si>
+  <si>
+    <t>mtv_verify_migration</t>
+  </si>
+  <si>
     <t>get_cluster_info</t>
   </si>
   <si>
@@ -1091,6 +1142,42 @@
     <t>•  Approval-gated provisioning: submit to ServiceNow, provision automatically once the change is approved</t>
   </si>
   <si>
+    <t>Migrates virtual machines into OpenShift Virtualization using the Migration Toolkit for Virtualization (MTV/Forklift). Validates that MTV is genuinely usable — operator, providers, storage and network maps — discovers VMs on the source platform, groups a multi-VM selection into the plans MTV will accept, and executes migrations behind a change-approval gate with a stated rollback at every stage.</t>
+  </si>
+  <si>
+    <t>•  Validate MTV end to end: operator installed and Ready, providers connected, storage and network maps present and Ready</t>
+  </si>
+  <si>
+    <t>•  Report WHY readiness failed and what to change — an unmapped datastore is named, not merely counted</t>
+  </si>
+  <si>
+    <t>•  Discover VMs on a source provider (vSphere, oVirt, OpenStack, OVA) from MTV's inventory service</t>
+  </si>
+  <si>
+    <t>•  Report per VM the facts a migration decision turns on: power state, disk footprint, guest OS, and changed block tracking</t>
+  </si>
+  <si>
+    <t>•  Refuse warm migration where changed block tracking is off, with the reason, rather than failing later at plan validation</t>
+  </si>
+  <si>
+    <t>•  Group a multi-VM selection into the plans MTV actually accepts — warm/cold, provider, both maps and target namespace are plan-level</t>
+  </si>
+  <si>
+    <t>•  Create plans without moving anything: a plan validates first, which is the dry-run equivalent</t>
+  </si>
+  <si>
+    <t>•  Execute an approved migration and report per-VM, per-step transfer progress</t>
+  </si>
+  <si>
+    <t>•  Roll back at any stage, with the meaning of rollback stated for that stage before it is done</t>
+  </si>
+  <si>
+    <t>•  Never delete a source VM — a cold migration powers it off, and that is the way back</t>
+  </si>
+  <si>
+    <t>•  Verify migrated VMs are actually running, using the same phase rules as provisioned VMs</t>
+  </si>
+  <si>
     <t>Cluster-wide operations including cluster info, node health, namespace management, and generic Kubernetes resource operations.</t>
   </si>
   <si>
@@ -1385,7 +1472,7 @@
     <t>}</t>
   </si>
   <si>
-    <t>All 15 agents — paste straight into a client config</t>
+    <t>All 16 agents — paste straight into a client config</t>
   </si>
   <si>
     <t xml:space="preserve">    "tcs-multi-cluster-acm": {</t>
@@ -1433,6 +1520,12 @@
     <t xml:space="preserve">      "url": "https://mcp-dashboard-openshift-mcp.apps.openshift.caaslab.local/mcp/upgrade-lifecycle/sse",</t>
   </si>
   <si>
+    <t xml:space="preserve">    "tcs-vm-migration": {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      "url": "https://mcp-dashboard-openshift-mcp.apps.openshift.caaslab.local/mcp/vm-migration/sse",</t>
+  </si>
+  <si>
     <t xml:space="preserve">    "tcs-cluster-operations": {</t>
   </si>
   <si>
@@ -1475,7 +1568,7 @@
     <t xml:space="preserve">      "url": "https://mcp-dashboard-openshift-mcp.apps.openshift.caaslab.local/mcp/observability/sse",</t>
   </si>
   <si>
-    <t>Registering all 15 puts 177 tool definitions in front of the model at once. Workable, but selection degrades as the list grows — pick the two or three agents a given consumer actually needs.</t>
+    <t>Registering all 16 puts 189 tool definitions in front of the model at once. Workable, but selection degrades as the list grows — pick the two or three agents a given consumer actually needs.</t>
   </si>
   <si>
     <t>Python — MCP SDK</t>
@@ -1646,10 +1739,10 @@
     <t>Agents</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>177</t>
+    <t>16</t>
+  </si>
+  <si>
+    <t>189</t>
   </si>
   <si>
     <t>Categories</t>
@@ -1673,7 +1766,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-08-14</t>
+    <t>2026-08-31</t>
   </si>
   <si>
     <t>Source of truth</t>
@@ -2301,7 +2394,7 @@
   <sheetPr>
     <tabColor rgb="FF2563EB"/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -2486,30 +2579,30 @@
         <v>34</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="D13" s="5">
+        <v>12</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="D13" s="5">
-        <v>20</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>38</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>35</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>39</v>
       </c>
       <c r="D14" s="9">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>40</v>
@@ -2520,13 +2613,13 @@
         <v>41</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>42</v>
       </c>
       <c r="D15" s="5">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>43</v>
@@ -2537,30 +2630,30 @@
         <v>44</v>
       </c>
       <c r="B16" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="D16" s="9">
+        <v>27</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>46</v>
-      </c>
-      <c r="D16" s="9">
-        <v>6</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>49</v>
       </c>
       <c r="D17" s="5">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>50</v>
@@ -2571,13 +2664,13 @@
         <v>51</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>52</v>
       </c>
       <c r="D18" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>53</v>
@@ -2588,42 +2681,59 @@
         <v>54</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>55</v>
       </c>
       <c r="D19" s="5">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="21" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+    <row r="20" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-    </row>
-    <row r="23" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
+      <c r="B20" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
+      <c r="D20" s="9">
+        <v>9</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+    </row>
+    <row r="24" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A24:E24"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E5" r:id="rId1"/>
@@ -2641,6 +2751,7 @@
     <hyperlink ref="E17" r:id="rId13"/>
     <hyperlink ref="E18" r:id="rId14"/>
     <hyperlink ref="E19" r:id="rId15"/>
+    <hyperlink ref="E20" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2652,7 +2763,7 @@
   <sheetPr>
     <tabColor rgb="FF0891B2"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2662,7 +2773,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2670,7 +2781,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2681,13 +2792,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2698,10 +2809,10 @@
         <v>10</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2712,10 +2823,10 @@
         <v>13</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2726,10 +2837,10 @@
         <v>17</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2740,10 +2851,10 @@
         <v>20</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2754,10 +2865,10 @@
         <v>24</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2768,10 +2879,10 @@
         <v>27</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2782,10 +2893,10 @@
         <v>30</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2796,24 +2907,24 @@
         <v>33</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>37</v>
-      </c>
       <c r="C13" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2824,10 +2935,10 @@
         <v>40</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2838,24 +2949,24 @@
         <v>43</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>47</v>
-      </c>
       <c r="C16" s="11" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2866,10 +2977,10 @@
         <v>50</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2880,10 +2991,10 @@
         <v>53</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2894,25 +3005,39 @@
         <v>56</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="21" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B5" r:id="rId1"/>
@@ -2960,6 +3085,9 @@
     <hyperlink ref="B19" r:id="rId43"/>
     <hyperlink ref="C19" r:id="rId44"/>
     <hyperlink ref="D19" r:id="rId45"/>
+    <hyperlink ref="B20" r:id="rId46"/>
+    <hyperlink ref="C20" r:id="rId47"/>
+    <hyperlink ref="D20" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2971,7 +3099,7 @@
   <sheetPr>
     <tabColor rgb="FF7C3AED"/>
   </sheetPr>
-  <dimension ref="A1:E181"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -2983,7 +3111,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2992,7 +3120,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3010,10 +3138,10 @@
         <v>3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -3027,7 +3155,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>10</v>
@@ -3044,7 +3172,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>10</v>
@@ -3061,7 +3189,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>10</v>
@@ -3078,7 +3206,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>10</v>
@@ -3095,7 +3223,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>10</v>
@@ -3112,7 +3240,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>10</v>
@@ -3129,7 +3257,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>13</v>
@@ -3146,7 +3274,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>13</v>
@@ -3163,7 +3291,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>13</v>
@@ -3180,7 +3308,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>13</v>
@@ -3197,7 +3325,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>13</v>
@@ -3214,7 +3342,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>13</v>
@@ -3231,7 +3359,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>13</v>
@@ -3248,7 +3376,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>13</v>
@@ -3265,7 +3393,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>13</v>
@@ -3282,7 +3410,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>13</v>
@@ -3299,7 +3427,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>13</v>
@@ -3316,7 +3444,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>13</v>
@@ -3333,7 +3461,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>13</v>
@@ -3350,7 +3478,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>13</v>
@@ -3367,7 +3495,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>13</v>
@@ -3384,7 +3512,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>13</v>
@@ -3401,7 +3529,7 @@
         <v>15</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>17</v>
@@ -3418,7 +3546,7 @@
         <v>15</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>17</v>
@@ -3435,7 +3563,7 @@
         <v>15</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>17</v>
@@ -3452,7 +3580,7 @@
         <v>15</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>17</v>
@@ -3469,7 +3597,7 @@
         <v>15</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>17</v>
@@ -3486,7 +3614,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>20</v>
@@ -3503,7 +3631,7 @@
         <v>15</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>20</v>
@@ -3520,7 +3648,7 @@
         <v>15</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E34" s="11" t="s">
         <v>20</v>
@@ -3537,7 +3665,7 @@
         <v>15</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>20</v>
@@ -3554,7 +3682,7 @@
         <v>15</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>20</v>
@@ -3571,7 +3699,7 @@
         <v>15</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>20</v>
@@ -3588,7 +3716,7 @@
         <v>15</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>20</v>
@@ -3605,7 +3733,7 @@
         <v>15</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>20</v>
@@ -3622,7 +3750,7 @@
         <v>15</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E40" s="11" t="s">
         <v>20</v>
@@ -3639,7 +3767,7 @@
         <v>15</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>20</v>
@@ -3656,7 +3784,7 @@
         <v>15</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E42" s="11" t="s">
         <v>20</v>
@@ -3673,7 +3801,7 @@
         <v>15</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>20</v>
@@ -3690,7 +3818,7 @@
         <v>15</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E44" s="11" t="s">
         <v>20</v>
@@ -3707,7 +3835,7 @@
         <v>15</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>20</v>
@@ -3724,7 +3852,7 @@
         <v>15</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E46" s="11" t="s">
         <v>20</v>
@@ -3741,7 +3869,7 @@
         <v>15</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>20</v>
@@ -3758,7 +3886,7 @@
         <v>15</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E48" s="11" t="s">
         <v>20</v>
@@ -3775,7 +3903,7 @@
         <v>15</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>20</v>
@@ -3792,7 +3920,7 @@
         <v>15</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E50" s="11" t="s">
         <v>20</v>
@@ -3809,7 +3937,7 @@
         <v>15</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>20</v>
@@ -3826,7 +3954,7 @@
         <v>15</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E52" s="11" t="s">
         <v>20</v>
@@ -3843,7 +3971,7 @@
         <v>22</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>24</v>
@@ -3860,7 +3988,7 @@
         <v>22</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E54" s="11" t="s">
         <v>24</v>
@@ -3877,7 +4005,7 @@
         <v>22</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E55" s="7" t="s">
         <v>24</v>
@@ -3894,7 +4022,7 @@
         <v>22</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E56" s="11" t="s">
         <v>24</v>
@@ -3911,7 +4039,7 @@
         <v>22</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>24</v>
@@ -3928,7 +4056,7 @@
         <v>22</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E58" s="11" t="s">
         <v>24</v>
@@ -3945,7 +4073,7 @@
         <v>22</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>24</v>
@@ -3962,7 +4090,7 @@
         <v>22</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E60" s="11" t="s">
         <v>24</v>
@@ -3979,7 +4107,7 @@
         <v>22</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>24</v>
@@ -3996,7 +4124,7 @@
         <v>22</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E62" s="11" t="s">
         <v>24</v>
@@ -4013,7 +4141,7 @@
         <v>22</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>27</v>
@@ -4030,7 +4158,7 @@
         <v>22</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E64" s="11" t="s">
         <v>27</v>
@@ -4047,7 +4175,7 @@
         <v>22</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>27</v>
@@ -4064,7 +4192,7 @@
         <v>22</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E66" s="11" t="s">
         <v>27</v>
@@ -4081,7 +4209,7 @@
         <v>22</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E67" s="7" t="s">
         <v>27</v>
@@ -4098,7 +4226,7 @@
         <v>22</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E68" s="11" t="s">
         <v>30</v>
@@ -4115,7 +4243,7 @@
         <v>22</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>30</v>
@@ -4132,7 +4260,7 @@
         <v>22</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E70" s="11" t="s">
         <v>30</v>
@@ -4149,7 +4277,7 @@
         <v>22</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>33</v>
@@ -4166,7 +4294,7 @@
         <v>22</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E72" s="11" t="s">
         <v>33</v>
@@ -4183,7 +4311,7 @@
         <v>22</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E73" s="7" t="s">
         <v>33</v>
@@ -4200,7 +4328,7 @@
         <v>22</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E74" s="11" t="s">
         <v>33</v>
@@ -4217,7 +4345,7 @@
         <v>22</v>
       </c>
       <c r="D75" s="14" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E75" s="7" t="s">
         <v>33</v>
@@ -4234,7 +4362,7 @@
         <v>22</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E76" s="11" t="s">
         <v>33</v>
@@ -4251,7 +4379,7 @@
         <v>22</v>
       </c>
       <c r="D77" s="14" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E77" s="7" t="s">
         <v>33</v>
@@ -4268,7 +4396,7 @@
         <v>22</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E78" s="11" t="s">
         <v>33</v>
@@ -4285,7 +4413,7 @@
         <v>22</v>
       </c>
       <c r="D79" s="14" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E79" s="7" t="s">
         <v>33</v>
@@ -4302,7 +4430,7 @@
         <v>22</v>
       </c>
       <c r="D80" s="15" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E80" s="11" t="s">
         <v>33</v>
@@ -4313,16 +4441,16 @@
         <v>34</v>
       </c>
       <c r="B81" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D81" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="E81" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D81" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="E81" s="7" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -4330,16 +4458,16 @@
         <v>34</v>
       </c>
       <c r="B82" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D82" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="E82" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="C82" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D82" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="E82" s="11" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -4347,16 +4475,16 @@
         <v>34</v>
       </c>
       <c r="B83" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D83" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="E83" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D83" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="E83" s="7" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -4364,16 +4492,16 @@
         <v>34</v>
       </c>
       <c r="B84" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D84" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="E84" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D84" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="E84" s="11" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -4381,16 +4509,16 @@
         <v>34</v>
       </c>
       <c r="B85" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D85" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="E85" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D85" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="E85" s="7" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -4398,16 +4526,16 @@
         <v>34</v>
       </c>
       <c r="B86" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D86" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="E86" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="C86" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D86" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="E86" s="11" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -4415,16 +4543,16 @@
         <v>34</v>
       </c>
       <c r="B87" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D87" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="E87" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D87" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -4432,16 +4560,16 @@
         <v>34</v>
       </c>
       <c r="B88" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D88" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="E88" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="C88" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D88" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="E88" s="11" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -4449,16 +4577,16 @@
         <v>34</v>
       </c>
       <c r="B89" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D89" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="E89" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D89" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="E89" s="7" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -4466,16 +4594,16 @@
         <v>34</v>
       </c>
       <c r="B90" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D90" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="E90" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="C90" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D90" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="E90" s="11" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -4483,16 +4611,16 @@
         <v>34</v>
       </c>
       <c r="B91" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D91" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="E91" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D91" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="E91" s="7" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -4500,166 +4628,166 @@
         <v>34</v>
       </c>
       <c r="B92" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D92" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="E92" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="C92" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D92" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="E92" s="11" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D93" s="14" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D94" s="15" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E94" s="11" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D95" s="14" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D96" s="15" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E96" s="11" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D97" s="14" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D98" s="15" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E98" s="11" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D99" s="14" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D100" s="15" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E100" s="11" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D101" s="14" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="E101" s="7" t="s">
         <v>40</v>
@@ -4667,16 +4795,16 @@
     </row>
     <row r="102" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B102" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D102" s="15" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E102" s="11" t="s">
         <v>40</v>
@@ -4684,16 +4812,16 @@
     </row>
     <row r="103" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D103" s="14" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E103" s="7" t="s">
         <v>40</v>
@@ -4701,16 +4829,16 @@
     </row>
     <row r="104" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B104" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D104" s="15" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E104" s="11" t="s">
         <v>40</v>
@@ -4718,16 +4846,16 @@
     </row>
     <row r="105" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D105" s="14" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E105" s="7" t="s">
         <v>40</v>
@@ -4735,16 +4863,16 @@
     </row>
     <row r="106" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B106" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D106" s="15" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E106" s="11" t="s">
         <v>40</v>
@@ -4752,16 +4880,16 @@
     </row>
     <row r="107" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D107" s="14" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="E107" s="7" t="s">
         <v>40</v>
@@ -4769,16 +4897,16 @@
     </row>
     <row r="108" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B108" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D108" s="15" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E108" s="11" t="s">
         <v>40</v>
@@ -4786,16 +4914,16 @@
     </row>
     <row r="109" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D109" s="14" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E109" s="7" t="s">
         <v>40</v>
@@ -4803,16 +4931,16 @@
     </row>
     <row r="110" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B110" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D110" s="15" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E110" s="11" t="s">
         <v>40</v>
@@ -4820,36 +4948,36 @@
     </row>
     <row r="111" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D111" s="14" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B112" s="10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D112" s="15" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E112" s="11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -4860,10 +4988,10 @@
         <v>42</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D113" s="14" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E113" s="7" t="s">
         <v>43</v>
@@ -4877,10 +5005,10 @@
         <v>42</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D114" s="15" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E114" s="11" t="s">
         <v>43</v>
@@ -4894,10 +5022,10 @@
         <v>42</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D115" s="14" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E115" s="7" t="s">
         <v>43</v>
@@ -4911,10 +5039,10 @@
         <v>42</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D116" s="15" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="E116" s="11" t="s">
         <v>43</v>
@@ -4928,10 +5056,10 @@
         <v>42</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D117" s="14" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E117" s="7" t="s">
         <v>43</v>
@@ -4945,10 +5073,10 @@
         <v>42</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D118" s="15" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="E118" s="11" t="s">
         <v>43</v>
@@ -4962,10 +5090,10 @@
         <v>42</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D119" s="14" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E119" s="7" t="s">
         <v>43</v>
@@ -4979,10 +5107,10 @@
         <v>42</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D120" s="15" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E120" s="11" t="s">
         <v>43</v>
@@ -4996,10 +5124,10 @@
         <v>42</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D121" s="14" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E121" s="7" t="s">
         <v>43</v>
@@ -5013,10 +5141,10 @@
         <v>42</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D122" s="15" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E122" s="11" t="s">
         <v>43</v>
@@ -5024,257 +5152,257 @@
     </row>
     <row r="123" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D123" s="14" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="8" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B124" s="10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D124" s="15" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E124" s="11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D125" s="14" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="8" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B126" s="10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D126" s="15" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E126" s="11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D127" s="14" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="8" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B128" s="10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D128" s="15" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="E128" s="11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D129" s="14" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="8" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D130" s="15" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E130" s="11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D131" s="14" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="8" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D132" s="15" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="E132" s="11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D133" s="14" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="E133" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="8" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D134" s="15" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="E134" s="11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D135" s="14" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="8" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D136" s="15" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E136" s="11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D137" s="14" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5282,16 +5410,16 @@
         <v>44</v>
       </c>
       <c r="B138" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C138" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D138" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="E138" s="11" t="s">
         <v>46</v>
-      </c>
-      <c r="C138" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D138" s="15" t="s">
-        <v>232</v>
-      </c>
-      <c r="E138" s="11" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5299,16 +5427,16 @@
         <v>44</v>
       </c>
       <c r="B139" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D139" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="E139" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="C139" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D139" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="E139" s="7" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5316,16 +5444,16 @@
         <v>44</v>
       </c>
       <c r="B140" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C140" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D140" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="E140" s="11" t="s">
         <v>46</v>
-      </c>
-      <c r="C140" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D140" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="E140" s="11" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5333,16 +5461,16 @@
         <v>44</v>
       </c>
       <c r="B141" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D141" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="E141" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D141" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="E141" s="7" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5350,16 +5478,16 @@
         <v>44</v>
       </c>
       <c r="B142" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C142" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D142" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="E142" s="11" t="s">
         <v>46</v>
-      </c>
-      <c r="C142" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D142" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="E142" s="11" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5367,132 +5495,132 @@
         <v>44</v>
       </c>
       <c r="B143" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D143" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="E143" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D143" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="E143" s="7" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B144" s="10" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D144" s="15" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="E144" s="11" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D145" s="14" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C146" s="9" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D146" s="15" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E146" s="11" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D147" s="14" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C148" s="9" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D148" s="15" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E148" s="11" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D149" s="14" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B150" s="10" t="s">
         <v>49</v>
       </c>
       <c r="C150" s="9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D150" s="15" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E150" s="11" t="s">
         <v>50</v>
@@ -5500,16 +5628,16 @@
     </row>
     <row r="151" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>49</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D151" s="14" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E151" s="7" t="s">
         <v>50</v>
@@ -5517,16 +5645,16 @@
     </row>
     <row r="152" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B152" s="10" t="s">
         <v>49</v>
       </c>
       <c r="C152" s="9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D152" s="15" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E152" s="11" t="s">
         <v>50</v>
@@ -5534,16 +5662,16 @@
     </row>
     <row r="153" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>49</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D153" s="14" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E153" s="7" t="s">
         <v>50</v>
@@ -5551,16 +5679,16 @@
     </row>
     <row r="154" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B154" s="10" t="s">
         <v>49</v>
       </c>
       <c r="C154" s="9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D154" s="15" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E154" s="11" t="s">
         <v>50</v>
@@ -5568,16 +5696,16 @@
     </row>
     <row r="155" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>49</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D155" s="14" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E155" s="7" t="s">
         <v>50</v>
@@ -5585,53 +5713,53 @@
     </row>
     <row r="156" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B156" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C156" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B156" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C156" s="9" t="s">
-        <v>45</v>
-      </c>
       <c r="D156" s="15" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E156" s="11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C157" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B157" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>45</v>
-      </c>
       <c r="D157" s="14" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E157" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B158" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C158" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B158" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C158" s="9" t="s">
-        <v>45</v>
-      </c>
       <c r="D158" s="15" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E158" s="11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5642,10 +5770,10 @@
         <v>52</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D159" s="14" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E159" s="7" t="s">
         <v>53</v>
@@ -5659,10 +5787,10 @@
         <v>52</v>
       </c>
       <c r="C160" s="9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D160" s="15" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E160" s="11" t="s">
         <v>53</v>
@@ -5676,10 +5804,10 @@
         <v>52</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D161" s="14" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E161" s="7" t="s">
         <v>53</v>
@@ -5693,10 +5821,10 @@
         <v>52</v>
       </c>
       <c r="C162" s="9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D162" s="15" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E162" s="11" t="s">
         <v>53</v>
@@ -5710,10 +5838,10 @@
         <v>52</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D163" s="14" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="E163" s="7" t="s">
         <v>53</v>
@@ -5727,10 +5855,10 @@
         <v>52</v>
       </c>
       <c r="C164" s="9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D164" s="15" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="E164" s="11" t="s">
         <v>53</v>
@@ -5744,10 +5872,10 @@
         <v>52</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D165" s="14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="E165" s="7" t="s">
         <v>53</v>
@@ -5761,10 +5889,10 @@
         <v>52</v>
       </c>
       <c r="C166" s="9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D166" s="15" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E166" s="11" t="s">
         <v>53</v>
@@ -5778,10 +5906,10 @@
         <v>52</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D167" s="14" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E167" s="7" t="s">
         <v>53</v>
@@ -5795,10 +5923,10 @@
         <v>52</v>
       </c>
       <c r="C168" s="9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D168" s="15" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E168" s="11" t="s">
         <v>53</v>
@@ -5812,10 +5940,10 @@
         <v>52</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D169" s="14" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="E169" s="7" t="s">
         <v>53</v>
@@ -5829,10 +5957,10 @@
         <v>52</v>
       </c>
       <c r="C170" s="9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D170" s="15" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E170" s="11" t="s">
         <v>53</v>
@@ -5840,36 +5968,36 @@
     </row>
     <row r="171" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D171" s="14" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E171" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="8" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B172" s="10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C172" s="9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D172" s="15" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E172" s="11" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5880,10 +6008,10 @@
         <v>55</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D173" s="14" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E173" s="7" t="s">
         <v>56</v>
@@ -5897,10 +6025,10 @@
         <v>55</v>
       </c>
       <c r="C174" s="9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D174" s="15" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E174" s="11" t="s">
         <v>56</v>
@@ -5914,10 +6042,10 @@
         <v>55</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D175" s="14" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="E175" s="7" t="s">
         <v>56</v>
@@ -5931,10 +6059,10 @@
         <v>55</v>
       </c>
       <c r="C176" s="9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D176" s="15" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E176" s="11" t="s">
         <v>56</v>
@@ -5948,10 +6076,10 @@
         <v>55</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D177" s="14" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E177" s="7" t="s">
         <v>56</v>
@@ -5965,10 +6093,10 @@
         <v>55</v>
       </c>
       <c r="C178" s="9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D178" s="15" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E178" s="11" t="s">
         <v>56</v>
@@ -5982,10 +6110,10 @@
         <v>55</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D179" s="14" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="E179" s="7" t="s">
         <v>56</v>
@@ -5999,10 +6127,10 @@
         <v>55</v>
       </c>
       <c r="C180" s="9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D180" s="15" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E180" s="11" t="s">
         <v>56</v>
@@ -6016,17 +6144,221 @@
         <v>55</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D181" s="14" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E181" s="7" t="s">
         <v>56</v>
       </c>
     </row>
+    <row r="182" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B182" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C182" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D182" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="E182" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="183" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D183" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="E183" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="184" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B184" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C184" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D184" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="E184" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="185" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D185" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="E185" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="186" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B186" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C186" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D186" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E186" s="11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="187" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D187" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="E187" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="188" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B188" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C188" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D188" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="E188" s="11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="189" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B189" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D189" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="E189" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="190" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B190" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C190" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D190" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="E190" s="11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="191" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D191" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="E191" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="192" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B192" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C192" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D192" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="E192" s="11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="193" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B193" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D193" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="E193" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E181"/>
+  <autoFilter ref="A4:E193"/>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
@@ -6209,6 +6541,18 @@
     <hyperlink ref="E179" r:id="rId175"/>
     <hyperlink ref="E180" r:id="rId176"/>
     <hyperlink ref="E181" r:id="rId177"/>
+    <hyperlink ref="E182" r:id="rId178"/>
+    <hyperlink ref="E183" r:id="rId179"/>
+    <hyperlink ref="E184" r:id="rId180"/>
+    <hyperlink ref="E185" r:id="rId181"/>
+    <hyperlink ref="E186" r:id="rId182"/>
+    <hyperlink ref="E187" r:id="rId183"/>
+    <hyperlink ref="E188" r:id="rId184"/>
+    <hyperlink ref="E189" r:id="rId185"/>
+    <hyperlink ref="E190" r:id="rId186"/>
+    <hyperlink ref="E191" r:id="rId187"/>
+    <hyperlink ref="E192" r:id="rId188"/>
+    <hyperlink ref="E193" r:id="rId189"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -6220,7 +6564,7 @@
   <sheetPr>
     <tabColor rgb="FF059669"/>
   </sheetPr>
-  <dimension ref="A1:D133"/>
+  <dimension ref="A1:D145"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -6231,7 +6575,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6239,7 +6583,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6253,10 +6597,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6267,94 +6611,94 @@
         <v>8</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6365,164 +6709,164 @@
         <v>8</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6533,80 +6877,80 @@
         <v>15</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6617,150 +6961,150 @@
         <v>15</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6771,80 +7115,80 @@
         <v>22</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6855,122 +7199,122 @@
         <v>22</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6981,136 +7325,136 @@
         <v>22</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
     </row>
     <row r="58" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
     </row>
     <row r="59" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D59" s="18" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
     </row>
     <row r="60" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>337</v>
+        <v>354</v>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
     </row>
     <row r="62" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
     </row>
     <row r="63" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
     </row>
     <row r="64" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>341</v>
+        <v>358</v>
       </c>
     </row>
     <row r="65" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D65" s="18" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -7121,192 +7465,192 @@
         <v>22</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
     </row>
     <row r="67" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D67" s="18" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
     </row>
     <row r="68" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>345</v>
+        <v>362</v>
       </c>
     </row>
     <row r="69" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D69" s="18" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
     </row>
     <row r="70" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D70" s="17" t="s">
-        <v>347</v>
+        <v>364</v>
       </c>
     </row>
     <row r="71" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D71" s="18" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
     </row>
     <row r="72" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D72" s="17" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
     </row>
     <row r="73" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D73" s="18" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
     </row>
     <row r="74" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
     </row>
     <row r="75" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D75" s="18" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
     </row>
     <row r="76" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D76" s="17" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
     </row>
     <row r="77" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D77" s="18" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
     </row>
     <row r="78" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D78" s="17" t="s">
-        <v>355</v>
+        <v>372</v>
       </c>
     </row>
     <row r="79" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D79" s="18" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
     </row>
     <row r="80" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -7314,755 +7658,923 @@
         <v>34</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>357</v>
+        <v>374</v>
       </c>
     </row>
     <row r="81" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D81" s="18" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
     </row>
     <row r="82" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D82" s="17" t="s">
-        <v>359</v>
+        <v>376</v>
       </c>
     </row>
     <row r="83" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D83" s="18" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
     </row>
     <row r="84" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D84" s="17" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
     </row>
     <row r="85" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D85" s="18" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
     </row>
     <row r="86" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D86" s="17" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
     </row>
     <row r="87" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>38</v>
+        <v>299</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>35</v>
+        <v>299</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>364</v>
+        <v>299</v>
+      </c>
+      <c r="D87" s="18" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="88" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D88" s="17" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
     </row>
     <row r="89" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D89" s="18" t="s">
-        <v>366</v>
+        <v>383</v>
       </c>
     </row>
     <row r="90" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D90" s="17" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
     </row>
     <row r="91" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D91" s="18" t="s">
-        <v>368</v>
+        <v>385</v>
       </c>
     </row>
     <row r="92" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
-        <v>282</v>
+        <v>37</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>282</v>
+        <v>38</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="D92" s="17" t="s">
-        <v>369</v>
+        <v>297</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="93" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D93" s="18" t="s">
-        <v>370</v>
+        <v>387</v>
       </c>
     </row>
     <row r="94" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D94" s="17" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
     </row>
     <row r="95" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>41</v>
+        <v>299</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>35</v>
+        <v>299</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="D95" s="5" t="s">
-        <v>372</v>
+        <v>299</v>
+      </c>
+      <c r="D95" s="18" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="96" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D96" s="17" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
     </row>
     <row r="97" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D97" s="18" t="s">
-        <v>374</v>
+        <v>391</v>
       </c>
     </row>
     <row r="98" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D98" s="17" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
     </row>
     <row r="99" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>282</v>
+        <v>41</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>282</v>
+        <v>38</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="D99" s="18" t="s">
-        <v>376</v>
+        <v>297</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="100" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D100" s="17" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
     </row>
     <row r="101" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D101" s="18" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
     </row>
     <row r="102" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D102" s="17" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
     </row>
     <row r="103" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>44</v>
+        <v>299</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>45</v>
+        <v>299</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="D103" s="5" t="s">
-        <v>380</v>
+        <v>299</v>
+      </c>
+      <c r="D103" s="18" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="104" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D104" s="17" t="s">
-        <v>381</v>
+        <v>398</v>
       </c>
     </row>
     <row r="105" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D105" s="18" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
     </row>
     <row r="106" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D106" s="17" t="s">
-        <v>383</v>
+        <v>400</v>
       </c>
     </row>
     <row r="107" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>282</v>
+        <v>44</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>282</v>
+        <v>38</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="D107" s="18" t="s">
-        <v>384</v>
+        <v>297</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="108" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D108" s="17" t="s">
-        <v>385</v>
+        <v>402</v>
       </c>
     </row>
     <row r="109" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>48</v>
+        <v>299</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>45</v>
+        <v>299</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="D109" s="5" t="s">
-        <v>386</v>
+        <v>299</v>
+      </c>
+      <c r="D109" s="18" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="110" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D110" s="17" t="s">
-        <v>387</v>
+        <v>404</v>
       </c>
     </row>
     <row r="111" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D111" s="18" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
     </row>
     <row r="112" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D112" s="17" t="s">
-        <v>389</v>
+        <v>406</v>
       </c>
     </row>
     <row r="113" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D113" s="18" t="s">
-        <v>390</v>
+        <v>407</v>
       </c>
     </row>
     <row r="114" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D114" s="17" t="s">
-        <v>391</v>
+        <v>408</v>
       </c>
     </row>
     <row r="115" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>282</v>
+        <v>47</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>282</v>
+        <v>48</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="D115" s="18" t="s">
-        <v>392</v>
+        <v>297</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="116" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D116" s="17" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
     </row>
     <row r="117" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>51</v>
+        <v>299</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>45</v>
+        <v>299</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="D117" s="5" t="s">
-        <v>394</v>
+        <v>299</v>
+      </c>
+      <c r="D117" s="18" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="118" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D118" s="17" t="s">
-        <v>395</v>
+        <v>412</v>
       </c>
     </row>
     <row r="119" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D119" s="18" t="s">
-        <v>396</v>
+        <v>413</v>
       </c>
     </row>
     <row r="120" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D120" s="17" t="s">
-        <v>397</v>
+        <v>414</v>
       </c>
     </row>
     <row r="121" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>282</v>
+        <v>51</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>282</v>
+        <v>48</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="D121" s="18" t="s">
-        <v>398</v>
+        <v>297</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="122" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D122" s="17" t="s">
-        <v>399</v>
+        <v>416</v>
       </c>
     </row>
     <row r="123" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D123" s="18" t="s">
-        <v>400</v>
+        <v>417</v>
       </c>
     </row>
     <row r="124" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D124" s="17" t="s">
-        <v>401</v>
+        <v>418</v>
       </c>
     </row>
     <row r="125" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D125" s="18" t="s">
-        <v>402</v>
+        <v>419</v>
       </c>
     </row>
     <row r="126" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="8" t="s">
-        <v>54</v>
+        <v>299</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>45</v>
+        <v>299</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="D126" s="9" t="s">
-        <v>403</v>
+        <v>299</v>
+      </c>
+      <c r="D126" s="17" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="127" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D127" s="18" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
     </row>
     <row r="128" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D128" s="17" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
     </row>
     <row r="129" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>282</v>
+        <v>54</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>282</v>
+        <v>48</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="D129" s="18" t="s">
-        <v>406</v>
+        <v>297</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="130" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D130" s="17" t="s">
-        <v>407</v>
+        <v>424</v>
       </c>
     </row>
     <row r="131" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D131" s="18" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
     </row>
     <row r="132" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="8" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B132" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D132" s="17" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
     </row>
     <row r="133" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D133" s="18" t="s">
-        <v>410</v>
+        <v>427</v>
+      </c>
+    </row>
+    <row r="134" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="B134" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="C134" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="D134" s="17" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="135" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D135" s="18" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="136" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="B136" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="C136" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="D136" s="17" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="137" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D137" s="18" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="138" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B138" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C138" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="D138" s="9" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="139" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D139" s="18" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="140" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="B140" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="C140" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="D140" s="17" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="141" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D141" s="18" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="142" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="B142" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="C142" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="D142" s="17" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="143" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D143" s="18" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="144" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="B144" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="C144" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="D144" s="17" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="145" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D145" s="18" t="s">
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -8089,139 +8601,139 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>411</v>
+        <v>440</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>412</v>
+        <v>441</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>413</v>
+        <v>442</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>414</v>
+        <v>443</v>
       </c>
     </row>
     <row r="5" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>415</v>
+        <v>444</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>416</v>
+        <v>445</v>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>417</v>
+        <v>446</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>418</v>
+        <v>447</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>419</v>
+        <v>448</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>420</v>
+        <v>449</v>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>421</v>
+        <v>450</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>422</v>
+        <v>451</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>423</v>
+        <v>452</v>
       </c>
       <c r="B10" s="13"/>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>424</v>
+        <v>453</v>
       </c>
       <c r="B12" s="19"/>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>425</v>
+        <v>454</v>
       </c>
       <c r="B13" s="19"/>
     </row>
     <row r="15" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
-        <v>426</v>
+        <v>455</v>
       </c>
       <c r="B15" s="20"/>
     </row>
     <row r="17" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>427</v>
+        <v>456</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>428</v>
+        <v>457</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>429</v>
+        <v>458</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>430</v>
+        <v>459</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>431</v>
+        <v>460</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>432</v>
+        <v>461</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>433</v>
+        <v>462</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>434</v>
+        <v>463</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>435</v>
+        <v>464</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>436</v>
+        <v>465</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>437</v>
+        <v>466</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>438</v>
+        <v>467</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>439</v>
+        <v>468</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>440</v>
+        <v>469</v>
       </c>
     </row>
     <row r="25" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>441</v>
+        <v>470</v>
       </c>
       <c r="B25" s="12"/>
     </row>
@@ -8253,7 +8765,7 @@
   <sheetPr>
     <tabColor rgb="FF1E293B"/>
   </sheetPr>
-  <dimension ref="A1:A158"/>
+  <dimension ref="A1:A164"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="130" customWidth="1"/>
@@ -8261,737 +8773,767 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>442</v>
+        <v>471</v>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>443</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>444</v>
+        <v>473</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>445</v>
+        <v>474</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>446</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>447</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>448</v>
+        <v>477</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>449</v>
+        <v>478</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>450</v>
+        <v>479</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>451</v>
+        <v>480</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>452</v>
+        <v>481</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>453</v>
+        <v>482</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>454</v>
+        <v>483</v>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>455</v>
+        <v>484</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>445</v>
+        <v>474</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
-        <v>446</v>
+        <v>475</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
-        <v>456</v>
+        <v>485</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
-        <v>457</v>
+        <v>486</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>449</v>
+        <v>478</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>450</v>
+        <v>479</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
-        <v>451</v>
+        <v>480</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
-        <v>458</v>
+        <v>487</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
-        <v>459</v>
+        <v>488</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
-        <v>460</v>
+        <v>489</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
-        <v>449</v>
+        <v>478</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>450</v>
+        <v>479</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
-        <v>451</v>
+        <v>480</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
-        <v>458</v>
+        <v>487</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>461</v>
+        <v>490</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
-        <v>462</v>
+        <v>491</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>449</v>
+        <v>478</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>450</v>
+        <v>479</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>451</v>
+        <v>480</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
-        <v>458</v>
+        <v>487</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
-        <v>463</v>
+        <v>492</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
-        <v>464</v>
+        <v>493</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
-        <v>449</v>
+        <v>478</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
-        <v>450</v>
+        <v>479</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
-        <v>451</v>
+        <v>480</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
-        <v>458</v>
+        <v>487</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="19" t="s">
-        <v>465</v>
+        <v>494</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
-        <v>466</v>
+        <v>495</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
-        <v>449</v>
+        <v>478</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
-        <v>450</v>
+        <v>479</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
-        <v>451</v>
+        <v>480</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
-        <v>458</v>
+        <v>487</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
-        <v>467</v>
+        <v>496</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
-        <v>468</v>
+        <v>497</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="19" t="s">
-        <v>449</v>
+        <v>478</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
-        <v>450</v>
+        <v>479</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="19" t="s">
-        <v>451</v>
+        <v>480</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
-        <v>458</v>
+        <v>487</v>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="19" t="s">
-        <v>469</v>
+        <v>498</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
-        <v>470</v>
+        <v>499</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="19" t="s">
-        <v>449</v>
+        <v>478</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="19" t="s">
-        <v>450</v>
+        <v>479</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="19" t="s">
-        <v>451</v>
+        <v>480</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="19" t="s">
-        <v>458</v>
+        <v>487</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="19" t="s">
-        <v>447</v>
+        <v>476</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="19" t="s">
-        <v>448</v>
+        <v>477</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="19" t="s">
-        <v>449</v>
+        <v>478</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="19" t="s">
-        <v>450</v>
+        <v>479</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="19" t="s">
-        <v>451</v>
+        <v>480</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="19" t="s">
-        <v>458</v>
+        <v>487</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="19" t="s">
-        <v>471</v>
+        <v>500</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="19" t="s">
-        <v>472</v>
+        <v>501</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="19" t="s">
-        <v>449</v>
+        <v>478</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="19" t="s">
-        <v>450</v>
+        <v>479</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="19" t="s">
-        <v>451</v>
+        <v>480</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="19" t="s">
-        <v>458</v>
+        <v>487</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="19" t="s">
-        <v>473</v>
+        <v>502</v>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="19" t="s">
-        <v>474</v>
+        <v>503</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="19" t="s">
-        <v>449</v>
+        <v>478</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="19" t="s">
-        <v>450</v>
+        <v>479</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="19" t="s">
-        <v>451</v>
+        <v>480</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="19" t="s">
-        <v>458</v>
+        <v>487</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="19" t="s">
-        <v>475</v>
+        <v>504</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="19" t="s">
-        <v>476</v>
+        <v>505</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="19" t="s">
-        <v>449</v>
+        <v>478</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="19" t="s">
-        <v>450</v>
+        <v>479</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="19" t="s">
-        <v>451</v>
+        <v>480</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="19" t="s">
-        <v>458</v>
+        <v>487</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="19" t="s">
-        <v>477</v>
+        <v>506</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="19" t="s">
-        <v>478</v>
+        <v>507</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="19" t="s">
-        <v>449</v>
+        <v>478</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="19" t="s">
-        <v>450</v>
+        <v>479</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="19" t="s">
-        <v>451</v>
+        <v>480</v>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="19" t="s">
-        <v>458</v>
+        <v>487</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="19" t="s">
-        <v>479</v>
+        <v>508</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="19" t="s">
-        <v>480</v>
+        <v>509</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="19" t="s">
-        <v>449</v>
+        <v>478</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="19" t="s">
-        <v>450</v>
+        <v>479</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="19" t="s">
-        <v>451</v>
+        <v>480</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="19" t="s">
-        <v>458</v>
+        <v>487</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="19" t="s">
-        <v>481</v>
+        <v>510</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="19" t="s">
-        <v>482</v>
+        <v>511</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="19" t="s">
-        <v>449</v>
+        <v>478</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="19" t="s">
-        <v>450</v>
+        <v>479</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="19" t="s">
-        <v>451</v>
+        <v>480</v>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="19" t="s">
-        <v>458</v>
+        <v>487</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="19" t="s">
-        <v>483</v>
+        <v>512</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="19" t="s">
-        <v>484</v>
+        <v>513</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="19" t="s">
-        <v>449</v>
+        <v>478</v>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="19" t="s">
-        <v>450</v>
+        <v>479</v>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="19" t="s">
-        <v>451</v>
+        <v>480</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="19" t="s">
-        <v>452</v>
+        <v>487</v>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="19" t="s">
-        <v>453</v>
+        <v>514</v>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="19" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="114" ht="34" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" s="13" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="116" ht="34" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" s="21" t="s">
-        <v>486</v>
+        <v>515</v>
+      </c>
+    </row>
+    <row r="113" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="19" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="114" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="19" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="115" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="19" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="116" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="19" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="117" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="19" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="19" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="119" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" s="19" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="120" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" s="19" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="121" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" s="19" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="122" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" s="19" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="123" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" s="19" t="s">
-        <v>282</v>
+        <v>483</v>
+      </c>
+    </row>
+    <row r="120" ht="34" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="13" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="122" ht="34" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="21" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="124" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="19" t="s">
-        <v>491</v>
+        <v>518</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="19" t="s">
-        <v>492</v>
+        <v>519</v>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="19" t="s">
-        <v>493</v>
+        <v>299</v>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="19" t="s">
-        <v>494</v>
+        <v>520</v>
       </c>
     </row>
     <row r="128" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="19" t="s">
-        <v>495</v>
+        <v>521</v>
       </c>
     </row>
     <row r="129" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="19" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="19" t="s">
-        <v>496</v>
+        <v>522</v>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="19" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="133" ht="34" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" s="21" t="s">
-        <v>498</v>
+        <v>523</v>
+      </c>
+    </row>
+    <row r="132" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="19" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="133" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="19" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="134" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="19" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="19" t="s">
-        <v>499</v>
+        <v>299</v>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="19" t="s">
-        <v>282</v>
+        <v>527</v>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="19" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="138" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A138" s="19" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="139" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" s="19" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="140" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" s="19" t="s">
-        <v>503</v>
+        <v>528</v>
+      </c>
+    </row>
+    <row r="139" ht="34" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="21" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="141" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="19" t="s">
-        <v>504</v>
+        <v>530</v>
       </c>
     </row>
     <row r="142" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="19" t="s">
-        <v>458</v>
+        <v>299</v>
       </c>
     </row>
     <row r="143" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="19" t="s">
-        <v>505</v>
+        <v>531</v>
       </c>
     </row>
     <row r="144" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="19" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="19" t="s">
-        <v>503</v>
+        <v>533</v>
       </c>
     </row>
     <row r="146" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="19" t="s">
-        <v>504</v>
+        <v>534</v>
       </c>
     </row>
     <row r="147" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="19" t="s">
-        <v>458</v>
+        <v>535</v>
       </c>
     </row>
     <row r="148" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="19" t="s">
-        <v>507</v>
+        <v>487</v>
       </c>
     </row>
     <row r="149" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="19" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="151" ht="34" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A151" s="16" t="s">
-        <v>509</v>
+        <v>536</v>
+      </c>
+    </row>
+    <row r="150" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="19" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="151" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" s="19" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="152" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="19" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="153" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="19" t="s">
-        <v>510</v>
+        <v>487</v>
       </c>
     </row>
     <row r="154" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="19" t="s">
-        <v>511</v>
+        <v>538</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="19" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="156" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A156" s="19" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="157" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157" s="19" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="158" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" s="19" t="s">
-        <v>513</v>
+        <v>539</v>
+      </c>
+    </row>
+    <row r="157" ht="34" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="16" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="159" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" s="19" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="160" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" s="19" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="161" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" s="19" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="162" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" s="19" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="163" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" s="19" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="164" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" s="19" t="s">
+        <v>544</v>
       </c>
     </row>
   </sheetData>
@@ -9015,43 +9557,43 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>514</v>
+        <v>545</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>515</v>
+        <v>546</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>516</v>
+        <v>547</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>517</v>
+        <v>548</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>518</v>
+        <v>549</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>519</v>
+        <v>550</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>520</v>
+        <v>551</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>32</v>
@@ -9062,29 +9604,29 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>521</v>
+        <v>552</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>522</v>
+        <v>553</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>523</v>
+        <v>554</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>12</v>
@@ -9095,7 +9637,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>524</v>
+        <v>555</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>23</v>
@@ -9106,18 +9648,18 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>525</v>
+        <v>556</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>526</v>
+        <v>557</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>26</v>
@@ -9128,7 +9670,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>527</v>
+        <v>558</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>19</v>
@@ -9139,7 +9681,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>528</v>
+        <v>559</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>29</v>
@@ -9150,7 +9692,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>529</v>
+        <v>560</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>9</v>
@@ -9161,40 +9703,40 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>530</v>
+        <v>561</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>531</v>
+        <v>562</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>532</v>
+        <v>563</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>533</v>
+        <v>564</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>16</v>
@@ -9205,7 +9747,7 @@
     </row>
     <row r="21" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
-        <v>534</v>
+        <v>565</v>
       </c>
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
@@ -9252,40 +9794,40 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>535</v>
+        <v>566</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>536</v>
+        <v>567</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>414</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>537</v>
+        <v>568</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>538</v>
+        <v>569</v>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>539</v>
+        <v>570</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>540</v>
+        <v>571</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>541</v>
+        <v>572</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>542</v>
+        <v>573</v>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -9293,68 +9835,68 @@
         <v>5</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>543</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>544</v>
+        <v>575</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>545</v>
+        <v>576</v>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>546</v>
+        <v>577</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>547</v>
+        <v>578</v>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>548</v>
+        <v>579</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>549</v>
+        <v>580</v>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>550</v>
+        <v>581</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>551</v>
+        <v>582</v>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>552</v>
+        <v>583</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>553</v>
+        <v>584</v>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>554</v>
+        <v>585</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>555</v>
+        <v>586</v>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>556</v>
+        <v>587</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>557</v>
+        <v>588</v>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>558</v>
+        <v>589</v>
       </c>
       <c r="B16" s="13"/>
     </row>
